--- a/artfynd/A 17648-2024 artfynd.xlsx
+++ b/artfynd/A 17648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121524099</v>
+        <v>121524143</v>
       </c>
       <c r="B2" t="n">
-        <v>56248</v>
+        <v>56249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,42 +791,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121524104</v>
+        <v>121524103</v>
       </c>
       <c r="B3" t="n">
-        <v>56269</v>
+        <v>56268</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -910,7 +910,7 @@
         <v>121524101</v>
       </c>
       <c r="B4" t="n">
-        <v>56255</v>
+        <v>56256</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,42 +1023,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121524103</v>
+        <v>121524104</v>
       </c>
       <c r="B5" t="n">
-        <v>56267</v>
+        <v>56270</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 17648-2024 artfynd.xlsx
+++ b/artfynd/A 17648-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121524143</v>
       </c>
       <c r="B2" t="n">
-        <v>56249</v>
+        <v>56250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,42 +791,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121524103</v>
+        <v>121524104</v>
       </c>
       <c r="B3" t="n">
-        <v>56268</v>
+        <v>56271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -907,14 +907,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121524101</v>
+        <v>121524103</v>
       </c>
       <c r="B4" t="n">
-        <v>56256</v>
+        <v>56269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -923,26 +923,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121524104</v>
+        <v>121524145</v>
       </c>
       <c r="B5" t="n">
-        <v>56270</v>
+        <v>56257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,30 +1035,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 17648-2024 artfynd.xlsx
+++ b/artfynd/A 17648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121524143</v>
+        <v>121524145</v>
       </c>
       <c r="B2" t="n">
-        <v>56250</v>
+        <v>56257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121524104</v>
+        <v>121524099</v>
       </c>
       <c r="B3" t="n">
-        <v>56271</v>
+        <v>56250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -907,42 +907,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121524103</v>
+        <v>121524104</v>
       </c>
       <c r="B4" t="n">
-        <v>56269</v>
+        <v>56271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1023,14 +1023,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121524145</v>
+        <v>121524103</v>
       </c>
       <c r="B5" t="n">
-        <v>56257</v>
+        <v>56269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1039,26 +1039,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 17648-2024 artfynd.xlsx
+++ b/artfynd/A 17648-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121524145</v>
+        <v>121524101</v>
       </c>
       <c r="B2" t="n">
         <v>56257</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121524099</v>
+        <v>121524143</v>
       </c>
       <c r="B3" t="n">
         <v>56250</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 17648-2024 artfynd.xlsx
+++ b/artfynd/A 17648-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121524101</v>
+        <v>121524145</v>
       </c>
       <c r="B2" t="n">
         <v>56257</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121524143</v>
+        <v>121524099</v>
       </c>
       <c r="B3" t="n">
         <v>56250</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,42 +907,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121524104</v>
+        <v>121524103</v>
       </c>
       <c r="B4" t="n">
-        <v>56271</v>
+        <v>56269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1023,42 +1023,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121524103</v>
+        <v>121524104</v>
       </c>
       <c r="B5" t="n">
-        <v>56269</v>
+        <v>56271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 17648-2024 artfynd.xlsx
+++ b/artfynd/A 17648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121524145</v>
+        <v>121524099</v>
       </c>
       <c r="B2" t="n">
-        <v>56257</v>
+        <v>56251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121524099</v>
+        <v>121524101</v>
       </c>
       <c r="B3" t="n">
-        <v>56250</v>
+        <v>56258</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,30 +803,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -910,7 +910,7 @@
         <v>121524103</v>
       </c>
       <c r="B4" t="n">
-        <v>56269</v>
+        <v>56270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>121524104</v>
       </c>
       <c r="B5" t="n">
-        <v>56271</v>
+        <v>56272</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 17648-2024 artfynd.xlsx
+++ b/artfynd/A 17648-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121524145</v>
+        <v>121524101</v>
       </c>
       <c r="B2" t="n">
         <v>56258</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 17648-2024 artfynd.xlsx
+++ b/artfynd/A 17648-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121524101</v>
+        <v>121524104</v>
       </c>
       <c r="B2" t="n">
-        <v>56258</v>
+        <v>56272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>206002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121524143</v>
+        <v>121524145</v>
       </c>
       <c r="B3" t="n">
-        <v>56251</v>
+        <v>56258</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,30 +803,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -907,42 +907,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121524104</v>
+        <v>121524103</v>
       </c>
       <c r="B4" t="n">
-        <v>56272</v>
+        <v>56270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1023,42 +1023,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121524103</v>
+        <v>121524099</v>
       </c>
       <c r="B5" t="n">
-        <v>56270</v>
+        <v>56251</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 17648-2024 artfynd.xlsx
+++ b/artfynd/A 17648-2024 artfynd.xlsx
@@ -1026,12 +1026,7 @@
         <v>121524103</v>
       </c>
       <c r="B5" t="n">
-        <v>56270</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56747</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17648-2024 artfynd.xlsx
+++ b/artfynd/A 17648-2024 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121524143</v>
+        <v>121524101</v>
       </c>
       <c r="B2" t="n">
-        <v>56251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -759,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,42 +786,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121524104</v>
+        <v>121524103</v>
       </c>
       <c r="B3" t="n">
-        <v>56272</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -907,42 +897,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121524145</v>
+        <v>121524099</v>
       </c>
       <c r="B4" t="n">
-        <v>56258</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -991,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +1008,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121524103</v>
+        <v>121524104</v>
       </c>
       <c r="B5" t="n">
-        <v>56767</v>
+        <v>56837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/artfynd/A 17648-2024 artfynd.xlsx
+++ b/artfynd/A 17648-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121524101</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121524103</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121524099</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,8 +1136,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121524104</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>